--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלירן בוזגלו - מחרוזת והלב 2026</v>
+        <v>שמעון בוסקילה - עולם יפה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411150&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411160&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלירן בוזגלו - מחרוזת והלב 2026</v>
+        <v>שמעון בוסקילה - עולם יפה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אביחי אוחנה - נתת לי חיים</v>
+        <v>קובי בוקעי - האהבה שלך</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411149&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411159&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-01</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אביחי אוחנה - נתת לי חיים</v>
+        <v>קובי בוקעי - האהבה שלך</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אבי בר - מחרוזת שקטים 2026</v>
+        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411148&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411158&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-01</v>
@@ -545,12 +545,278 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אבי בר - מחרוזת שקטים 2026</v>
+        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מיכל בן חיים - איזה עולם</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411157&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מיכל בן חיים - איזה עולם</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מורן מצליח - מאז שהלכת</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411156&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מורן מצליח - מאז שהלכת</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411155&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>איה - באתי לרקוד</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411154&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>איה - באתי לרקוד</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ישראל צוברי - אלוקיי</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411153&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ישראל צוברי - אלוקיי</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411152&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411151&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בוסקילה - עולם יפה</v>
+        <v>סטטיק &amp; רינת בר - אקסטרה לארג'</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411160&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411179&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בוסקילה - עולם יפה</v>
+        <v>סטטיק &amp; רינת בר - אקסטרה לארג'</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קובי בוקעי - האהבה שלך</v>
+        <v>רועי מזוז &amp; שילה בן אברהם - הסיפור של ג'וני</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411159&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411178&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קובי בוקעי - האהבה שלך</v>
+        <v>רועי מזוז &amp; שילה בן אברהם - הסיפור של ג'וני</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
+        <v>עופר סופר - טוב ומטיב</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411158&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411177&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
+        <v>עופר סופר - טוב ומטיב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מיכל בן חיים - איזה עולם</v>
+        <v>משינה - כמעט וכאילו</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411157&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411176&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מיכל בן חיים - איזה עולם</v>
+        <v>משינה - כמעט וכאילו</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מורן מצליח - מאז שהלכת</v>
+        <v>מיכאל כורש - שלוש בלילה</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411156&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411175&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מורן מצליח - מאז שהלכת</v>
+        <v>מיכאל כורש - שלוש בלילה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
+        <v>יובל לוי מארחת את דין פרינס גבאי - פאקים</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411155&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411174&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
+        <v>יובל לוי מארחת את דין פרינס גבאי - פאקים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>איה - באתי לרקוד</v>
+        <v>יובל לוי - החיה</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411154&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411173&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>איה - באתי לרקוד</v>
+        <v>יובל לוי - החיה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ישראל צוברי - אלוקיי</v>
+        <v>שניאור אוראל - שערי שמים פתח</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411153&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411172&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>ישראל צוברי - אלוקיי</v>
+        <v>שניאור אוראל - שערי שמים פתח</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
+        <v>מתנאל אסייג - תדר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411152&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411171&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
+        <v>מתנאל אסייג - תדר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
+        <v>ליאל אוחיון - היית גבר</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411151&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411170&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,12 +811,354 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
+        <v>ליאל אוחיון - היית גבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>ישראל ברששת - מחרוזת מהנשמה 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411169&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>ישראל ברששת - מחרוזת מהנשמה 2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>ישעיהו - תשמור חזק</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411168&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>ישעיהו - תשמור חזק</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>יוסף חיים - איש שחולם געגוע</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411167&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>יוסף חיים - איש שחולם געגוע</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>יהונתן ישראל - רק לעלות</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411166&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>יהונתן ישראל - רק לעלות</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>חן כהן - תל גיבורים</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411165&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>חן כהן - תל גיבורים</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>הייפ קרו - אהבה עיוורת</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411164&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>הייפ קרו - אהבה עיוורת</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אלינור חלילוב - מחרוזת קיץ 2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411163&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אלינור חלילוב - מחרוזת קיץ 2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>אברהם חתומה - כשהלב בקרשים</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411162&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>אברהם חתומה - כשהלב בקרשים</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>אביאלי חדד - וויסקי בלילות</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411161&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>אביאלי חדד - וויסקי בלילות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מירי מסיקה - לב לבן קאבר</v>
+        <v>שושנה קנו - שופוני</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411187&amp;sid=8c32dea66695624c346eddfe12cc9153</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411211&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מירי מסיקה - לב לבן קאבר</v>
+        <v>שושנה קנו - שופוני</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אמיר אליהו - כסף הכסף קאבר</v>
+        <v>רוני ידידיה מארח את לירון עמרם - ערב חצוי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411182&amp;sid=8c32dea66695624c346eddfe12cc9153</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411210&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,354 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אמיר אליהו - כסף הכסף קאבר</v>
+        <v>רוני ידידיה מארח את לירון עמרם - ערב חצוי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נוי מיהלי - רק תקופה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411209&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נוי מיהלי - רק תקופה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מתן חסן - בחורה לחתונה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411208&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מתן חסן - בחורה לחתונה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ליעד מאיר &amp; אופק אדנק - יוצאת מן הכלל</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411207&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ליעד מאיר &amp; אופק אדנק - יוצאת מן הכלל</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>לינור דהן - רצוא ושוב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411206&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>לינור דהן - רצוא ושוב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ליאור ברגר - כשאת לידי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411205&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ליאור ברגר - כשאת לידי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ידידיה חייט - עמוק בתוך הלב</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411204&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ידידיה חייט - עמוק בתוך הלב</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>גל ג'ומה - הילטון</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411203&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>גל ג'ומה - הילטון</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אליעד מלכי - שקיעות</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411202&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אליעד מלכי - שקיעות</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אבישי עוזיאל - תרקדי איתי עכשיו</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411201&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אבישי עוזיאל - תרקדי איתי עכשיו</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שושנה קנו - שופוני</v>
+        <v>שיר זוארץ - שיר של אהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411211&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411237&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שושנה קנו - שופוני</v>
+        <v>שיר זוארץ - שיר של אהבה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רוני ידידיה מארח את לירון עמרם - ערב חצוי</v>
+        <v>רמי מור - זה נגמר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411210&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411236&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רוני ידידיה מארח את לירון עמרם - ערב חצוי</v>
+        <v>רמי מור - זה נגמר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נוי מיהלי - רק תקופה</v>
+        <v>רונה גולד - רוקדת</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411209&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411235&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נוי מיהלי - רק תקופה</v>
+        <v>רונה גולד - רוקדת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מתן חסן - בחורה לחתונה</v>
+        <v>עידו כנפי - רק הזיכרון</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411208&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411234&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מתן חסן - בחורה לחתונה</v>
+        <v>עידו כנפי - רק הזיכרון</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליעד מאיר &amp; אופק אדנק - יוצאת מן הכלל</v>
+        <v>משה קליין - כל הטוב</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411207&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411233&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליעד מאיר &amp; אופק אדנק - יוצאת מן הכלל</v>
+        <v>משה קליין - כל הטוב</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>לינור דהן - רצוא ושוב</v>
+        <v>ירון בר - ודע שלעתיד</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411206&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411232&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>לינור דהן - רצוא ושוב</v>
+        <v>ירון בר - ודע שלעתיד</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ליאור ברגר - כשאת לידי</v>
+        <v>זוהר חודדי - תמיד שמח קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411205&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411231&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ליאור ברגר - כשאת לידי</v>
+        <v>זוהר חודדי - תמיד שמח קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ידידיה חייט - עמוק בתוך הלב</v>
+        <v>התחנה האחרונה - המנון גביע שווגר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411204&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411230&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>ידידיה חייט - עמוק בתוך הלב</v>
+        <v>התחנה האחרונה - המנון גביע שווגר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>גל ג'ומה - הילטון</v>
+        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן - וויסקי</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411203&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411229&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>גל ג'ומה - הילטון</v>
+        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן - וויסקי</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אליעד מלכי - שקיעות</v>
+        <v>דניאל אביב - לאיבוד</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411202&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411228&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אליעד מלכי - שקיעות</v>
+        <v>דניאל אביב - לאיבוד</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אבישי עוזיאל - תרקדי איתי עכשיו</v>
+        <v>אורי זר - את באה ונגעת</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411201&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411227&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,12 +849,544 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אבישי עוזיאל - תרקדי איתי עכשיו</v>
+        <v>אורי זר - את באה ונגעת</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אדיר ניזרי - מחרוזת זה הרגע 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411226&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אדיר ניזרי - מחרוזת זה הרגע 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אדיר ניזרי - מחרוזת בית״ר הדגל של המדינה 2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411225&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אדיר ניזרי - מחרוזת בית״ר הדגל של המדינה 2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אדיר ניזרי - מחרוזת אני אוהב אותך בית״ר 2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411224&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אדיר ניזרי - מחרוזת אני אוהב אותך בית״ר 2026</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>מור זיתוני - באתי הביתה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411223&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>מור זיתוני - באתי הביתה</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>מאור בן חיים - סימן קטן</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411222&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>מאור בן חיים - סימן קטן</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ליאל אברהם - שנינו כאן</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411221&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>ליאל אברהם - שנינו כאן</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ינון טייב - ויהי בנסוע הארון</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411220&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>ינון טייב - ויהי בנסוע הארון</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>יוני גרייב - אם את עוד אוהבת</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411219&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>יוני גרייב - אם את עוד אוהבת</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>דורון הברי - התיקון שלך</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411218&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>דורון הברי - התיקון שלך</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>דולב שמחי - השם שלך</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411217&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>דולב שמחי - השם שלך</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>בן עשור - הרי את מקודשת</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C23" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411216&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>בן עשור - הרי את מקודשת</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>בן מצמבר - עד מתי</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C24" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411215&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>בן מצמבר - עד מתי</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>ארי בן מתתיהו שלי - ירושלים בליבי</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C25" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411214&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>ארי בן מתתיהו שלי - ירושלים בליבי</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>אורין צדקיהו - בייבי</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C26" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411213&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>אורין צדקיהו - בייבי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L26"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אדיר ניזרי - מחרוזת החשמל חוזר אל הבירה 2026</v>
+        <v>להקת דרך - זה הזמן</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411241&amp;sid=83040952a8788a385111ace586a8d065</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411256&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אדיר ניזרי - מחרוזת החשמל חוזר אל הבירה 2026</v>
+        <v>להקת דרך - זה הזמן</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אליאור נונה - מחרוזת הראש נדלק 2026</v>
+        <v>חגית ביטון חג'בי - An Optimic Day</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411240&amp;sid=83040952a8788a385111ace586a8d065</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411255&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,240 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אליאור נונה - מחרוזת הראש נדלק 2026</v>
+        <v>חגית ביטון חג'בי - An Optimic Day</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>הדר אבני - בואי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411254&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>הדר אבני - בואי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>גיל ישראלוב &amp; שימי יונייב ותזמורתו - מחרוזת יאסו טאנץ 2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411253&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>גיל ישראלוב &amp; שימי יונייב ותזמורתו - מחרוזת יאסו טאנץ 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ג'ולי עידן - פרידה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411252&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ג'ולי עידן - פרידה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>בן ארצי - אינטימיות בזמן כאוטי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411251&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>בן ארצי - אינטימיות בזמן כאוטי</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלקנה אלפסי - מחפש משמעות</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411250&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלקנה אלפסי - מחפש משמעות</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אלעד אלדד - תגיד תודה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411249&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אלעד אלדד - תגיד תודה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-06-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>להקת דרך - זה הזמן</v>
+        <v>שיראל חדד - קנאה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411256&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411264&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-07</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>להקת דרך - זה הזמן</v>
+        <v>שיראל חדד - קנאה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>חגית ביטון חג'בי - An Optimic Day</v>
+        <v>רון שובל - תחת החופה</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411255&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411263&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-07</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>חגית ביטון חג'בי - An Optimic Day</v>
+        <v>רון שובל - תחת החופה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>הדר אבני - בואי</v>
+        <v>רון חיון - גבר מרוקאי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411254&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411262&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-07</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>הדר אבני - בואי</v>
+        <v>רון חיון - גבר מרוקאי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>גיל ישראלוב &amp; שימי יונייב ותזמורתו - מחרוזת יאסו טאנץ 2026</v>
+        <v>עמית אבני &amp; מאור כהן - עשרים וארבע</v>
       </c>
       <c r="B5" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411253&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411261&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-07</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>גיל ישראלוב &amp; שימי יונייב ותזמורתו - מחרוזת יאסו טאנץ 2026</v>
+        <v>עמית אבני &amp; מאור כהן - עשרים וארבע</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ג'ולי עידן - פרידה</v>
+        <v>סדריק מארח את אפק לאמור - רק רוצה לחיות פה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411252&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411260&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-07</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ג'ולי עידן - פרידה</v>
+        <v>סדריק מארח את אפק לאמור - רק רוצה לחיות פה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>בן ארצי - אינטימיות בזמן כאוטי</v>
+        <v>נתנאל מלכה - מי יחבק אותך</v>
       </c>
       <c r="B7" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411251&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411259&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-07</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>בן ארצי - אינטימיות בזמן כאוטי</v>
+        <v>נתנאל מלכה - מי יחבק אותך</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אלקנה אלפסי - מחפש משמעות</v>
+        <v>נשמה וקצב - בלעדיה</v>
       </c>
       <c r="B8" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411250&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411258&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-07</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אלקנה אלפסי - מחפש משמעות</v>
+        <v>נשמה וקצב - בלעדיה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אלעד אלדד - תגיד תודה</v>
+        <v>ניסים ברנס - הולך על בטוח</v>
       </c>
       <c r="B9" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411249&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411257&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-07</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אלעד אלדד - תגיד תודה</v>
+        <v>ניסים ברנס - הולך על בטוח</v>
       </c>
     </row>
   </sheetData>
